--- a/data/simpanan_transaksi.xlsx
+++ b/data/simpanan_transaksi.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -425,9 +425,9 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -481,36 +481,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7759aadc-eb94-479a-aaeb-536a291cca90</t>
+          <t>ea827b38-87f9-43eb-8087-4cf52776c21e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-16 15:05:55</t>
+          <t>2026-04-23 08:29:55</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hari Raya</t>
+          <t>Simpanan Pokok</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10000000</v>
+        <v>500000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -520,6 +520,771 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>d5c604e9-12f8-4f0d-bb2f-cb7bbc071216</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:30:46</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Simpanan Wajib</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>f785c550-3bc1-4345-8f14-4a738dbbbb54</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:31:13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Koperasi</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5bce0edd-9622-4d19-ad87-96b9d26eea12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:40:53</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b684890c-f2a8-459d-8fad-726ac5dad7e6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:41:09</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3f4542ff-0ca3-431d-8ecd-97218b67ee3c</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:41:22</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>062b317a-4dc8-4040-938f-7633733d5eb3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:42:29</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5790c3e3-7839-40f9-8aab-012ecbc5a4af</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:42:40</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7eb5c023-d067-4c4f-a40a-20315448a952</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-04-23 08:42:52</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Simpanan Pendidikan</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>de47886b-b48e-4361-92f9-d06cc51ac3a4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-04-23 09:53:22</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>67bdbe72-2c12-4be4-a858-bfb34a1f2818</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-04-23 09:53:33</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>62fac785-49bf-4d89-b772-f94b2029b76d</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-04-23 09:58:59</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>9a6620f9-9bf7-4953-9e9d-977075daf799</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-04-23 09:59:11</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Simpanan Pendidikan</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>b0d224d4-6f6d-44c4-9f4a-d12fd1afce46</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-04-23 10:28:31</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Simpanan Pokok</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>068386f1-fbd4-4f9f-8032-f5094ffe3e06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-04-23 10:29:14</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>a9f08235-f4b7-4d38-a740-522810a99f4a</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-04-23 13:39:37</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>9ab60756-2fc4-4178-b544-a57bf3cdc70c</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-04-23 13:51:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>b0e0ab57-3aea-42d9-ad2b-0f76993b3a3b</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-04-23 15:57:21</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Simpanan disetujui admin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>septiawan</t>
         </is>
       </c>
     </row>

--- a/data/simpanan_transaksi.xlsx
+++ b/data/simpanan_transaksi.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1288,6 +1288,51 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8663ef18-4318-47f9-8ddc-5a09ee432c39</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:12:50</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Simpanan disetujui admin</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/simpanan_transaksi.xlsx
+++ b/data/simpanan_transaksi.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1333,6 +1333,96 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bc6c5a53-d970-431d-9023-88328d06643b</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>02b98d05-e120-42e8-81b2-1fe8887d5c70</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AG0001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Budi Santoso</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:24:18</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Setoran via import Excel (append)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15b6bc31-fdf4-401d-8cb8-3eb650288e1a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0618aeab-d75c-487e-b4cb-e99b9609ef46</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AG0002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:24:18</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Simpanan Pendidikan</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Setoran via import Excel (append)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/simpanan_transaksi.xlsx
+++ b/data/simpanan_transaksi.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -481,32 +481,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>519dd162-13c1-43f8-9d80-9b8b30200e20</t>
+          <t>fde48b5d-b115-4fb7-8393-2c806626cdb7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGT-DEMO-001</t>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KOP-0001</t>
+          <t>AGT-001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anggota Demo</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04 10:27:13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manasuka</t>
+          <t>Simpanan Pokok</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -514,10 +514,100 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Simpanan Pokok validasi anggota baru</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bdba49f0-d9f9-4b1c-90a1-1878b300d925</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:39:21</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Simpanan disetujui admin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>boseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>133dfeaf-5717-44ed-855f-9d79206124bb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Anggota Demo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Setoran awal demo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>admin_koperasi</t>
         </is>

--- a/data/simpanan_transaksi.xlsx
+++ b/data/simpanan_transaksi.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -425,10 +425,10 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fde48b5d-b115-4fb7-8393-2c806626cdb7</t>
+          <t>8c7f9409-83d3-4e98-b356-92fb6da01504</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+          <t>7afc9502-af5e-4bf3-b468-6375c7569652</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-04 10:27:13</t>
+          <t>2026-05-21 16:02:07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -519,97 +519,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>super_admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bdba49f0-d9f9-4b1c-90a1-1878b300d925</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-04 10:39:21</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Simpanan Pensiun</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Simpanan disetujui admin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>boseng</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>133dfeaf-5717-44ed-855f-9d79206124bb</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AGT-DEMO-001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KOP-0001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Anggota Demo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Simpanan Manasuka</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Setoran awal demo</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>admin_koperasi</t>
+          <t>superadmin</t>
         </is>
       </c>
     </row>
